--- a/artfynd/A 60512-2024 artfynd.xlsx
+++ b/artfynd/A 60512-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>125801762</v>
       </c>
       <c r="B2" t="n">
-        <v>75058</v>
+        <v>75059</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,6 +779,220 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126021259</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91193</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Klashagen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>453800</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6610105</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lina Sundman Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lina Sundman Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126020959</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91193</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Klashagen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>453808</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6610083</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lina Sundman Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lina Sundman Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60512-2024 artfynd.xlsx
+++ b/artfynd/A 60512-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>126021259</v>
       </c>
       <c r="B3" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126020959</v>
       </c>
       <c r="B4" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60512-2024 artfynd.xlsx
+++ b/artfynd/A 60512-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125801762</v>
       </c>
       <c r="B2" t="n">
-        <v>75059</v>
+        <v>75060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126021259</v>
+        <v>126020959</v>
       </c>
       <c r="B3" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453800</v>
+        <v>453808</v>
       </c>
       <c r="R3" t="n">
-        <v>6610105</v>
+        <v>6610083</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126020959</v>
+        <v>126021259</v>
       </c>
       <c r="B4" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453808</v>
+        <v>453800</v>
       </c>
       <c r="R4" t="n">
-        <v>6610083</v>
+        <v>6610105</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 60512-2024 artfynd.xlsx
+++ b/artfynd/A 60512-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126020959</v>
+        <v>126021259</v>
       </c>
       <c r="B3" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453808</v>
+        <v>453800</v>
       </c>
       <c r="R3" t="n">
-        <v>6610083</v>
+        <v>6610105</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126021259</v>
+        <v>126020959</v>
       </c>
       <c r="B4" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453800</v>
+        <v>453808</v>
       </c>
       <c r="R4" t="n">
-        <v>6610105</v>
+        <v>6610083</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 60512-2024 artfynd.xlsx
+++ b/artfynd/A 60512-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>126021259</v>
       </c>
       <c r="B3" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126020959</v>
       </c>
       <c r="B4" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60512-2024 artfynd.xlsx
+++ b/artfynd/A 60512-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125801762</v>
       </c>
       <c r="B2" t="n">
-        <v>75060</v>
+        <v>75064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126021259</v>
       </c>
       <c r="B3" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126020959</v>
       </c>
       <c r="B4" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60512-2024 artfynd.xlsx
+++ b/artfynd/A 60512-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125801762</v>
       </c>
       <c r="B2" t="n">
-        <v>75064</v>
+        <v>75067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126021259</v>
       </c>
       <c r="B3" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126020959</v>
       </c>
       <c r="B4" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60512-2024 artfynd.xlsx
+++ b/artfynd/A 60512-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -994,6 +994,103 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127642254</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43939</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Klashagen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>453916</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6610144</v>
+      </c>
+      <c r="S5" t="n">
+        <v>38</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lina Sundman Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lina Sundman Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60512-2024 artfynd.xlsx
+++ b/artfynd/A 60512-2024 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>127642254</v>
       </c>
       <c r="B5" t="n">
-        <v>43939</v>
+        <v>43941</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60512-2024 artfynd.xlsx
+++ b/artfynd/A 60512-2024 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>127642254</v>
       </c>
       <c r="B5" t="n">
-        <v>43941</v>
+        <v>43942</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
